--- a/outputs/religion/religion_annotations_gold_flat.xlsx
+++ b/outputs/religion/religion_annotations_gold_flat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK105"/>
+  <dimension ref="A1:BR105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,41 @@
           <t>elongation</t>
         </is>
       </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>ironie</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>insulte</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>emoji</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>mépris / haine</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>argot</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>abréviation</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>interjection</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -842,22 +877,16 @@
           <t>pourquoi embête tu ma copine ?</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
@@ -937,6 +966,27 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1049,22 +1099,16 @@
           <t>elle a r demande</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
         <v>2</v>
       </c>
@@ -1144,6 +1188,27 @@
         <v>0</v>
       </c>
       <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1256,22 +1321,16 @@
           <t>c'est marrant de se moquer</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>Joie</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
@@ -1351,6 +1410,27 @@
         <v>0</v>
       </c>
       <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,22 +1543,16 @@
           <t>ptn la maturite</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
         <v>2</v>
       </c>
@@ -1559,6 +1633,27 @@
       </c>
       <c r="BK5" t="n">
         <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1665,15 +1760,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
         <v>3</v>
       </c>
@@ -1754,6 +1840,27 @@
       </c>
       <c r="BK6" t="n">
         <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1860,15 +1967,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="n">
         <v>1</v>
       </c>
@@ -1948,6 +2046,27 @@
         <v>0</v>
       </c>
       <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2055,15 +2174,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
         <v>1</v>
       </c>
@@ -2143,6 +2253,27 @@
         <v>0</v>
       </c>
       <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2255,22 +2386,16 @@
           <t>remettez vous en question</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="n">
         <v>1</v>
       </c>
@@ -2350,6 +2475,27 @@
         <v>0</v>
       </c>
       <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2457,15 +2603,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="n">
         <v>2</v>
       </c>
@@ -2545,6 +2682,27 @@
         <v>0</v>
       </c>
       <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2652,15 +2810,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="n">
         <v>1</v>
       </c>
@@ -2740,6 +2889,27 @@
         <v>0</v>
       </c>
       <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2857,7 +3027,6 @@
           <t>le juif</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>Dégoût</t>
@@ -2868,7 +3037,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -2879,7 +3047,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="n">
         <v>2</v>
       </c>
@@ -2959,6 +3126,27 @@
         <v>0</v>
       </c>
       <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3066,15 +3254,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
         <v>1</v>
       </c>
@@ -3154,6 +3333,27 @@
         <v>0</v>
       </c>
       <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3266,22 +3466,16 @@
           <t>on s'en fout de savoir qui croit quoi</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="n">
         <v>1</v>
       </c>
@@ -3361,6 +3555,27 @@
         <v>0</v>
       </c>
       <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3473,22 +3688,16 @@
           <t>elle etait fiere de lui</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>Fierté</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="n">
         <v>1</v>
       </c>
@@ -3568,6 +3777,27 @@
         <v>0</v>
       </c>
       <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3680,22 +3910,16 @@
           <t>Vs êtes complexés ou quoi pour lui parler comme ca</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="n">
         <v>3</v>
       </c>
@@ -3775,6 +3999,27 @@
         <v>0</v>
       </c>
       <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3887,22 +4132,16 @@
           <t>je suis fière de mon petit frère</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
           <t>Fierté</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
@@ -3982,6 +4221,27 @@
         <v>0</v>
       </c>
       <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4099,7 +4359,6 @@
           <t>nn</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -4110,7 +4369,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -4121,7 +4379,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="n">
         <v>2</v>
       </c>
@@ -4202,6 +4459,27 @@
       </c>
       <c r="BK18" t="n">
         <v>0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4313,22 +4591,16 @@
           <t>on s'en fou de sa vie ou de sa religion</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="n">
         <v>1</v>
       </c>
@@ -4408,6 +4680,27 @@
         <v>0</v>
       </c>
       <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4525,7 +4818,6 @@
           <t>on s'en tape de ce que vous pensez</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -4536,7 +4828,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -4547,7 +4838,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
         <v>2</v>
       </c>
@@ -4628,6 +4918,27 @@
       </c>
       <c r="BK20" t="n">
         <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -4739,22 +5050,16 @@
           <t>grv on s'en fou</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="n">
         <v>0</v>
       </c>
@@ -4834,6 +5139,27 @@
         <v>0</v>
       </c>
       <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4941,15 +5267,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
@@ -5029,6 +5346,27 @@
         <v>0</v>
       </c>
       <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5146,7 +5484,6 @@
           <t>elle s'en fou de ton avis</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -5157,7 +5494,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -5168,7 +5504,6 @@
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="n">
         <v>1</v>
       </c>
@@ -5248,6 +5583,27 @@
         <v>0</v>
       </c>
       <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5360,22 +5716,16 @@
           <t>laisse la tranquille</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="n">
         <v>1</v>
       </c>
@@ -5455,6 +5805,27 @@
         <v>0</v>
       </c>
       <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5567,22 +5938,16 @@
           <t>les moutons ça avance en troupeau</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="n">
         <v>4</v>
       </c>
@@ -5662,6 +6027,27 @@
         <v>0</v>
       </c>
       <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5769,15 +6155,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="n">
         <v>1</v>
       </c>
@@ -5857,6 +6234,27 @@
         <v>0</v>
       </c>
       <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5974,7 +6372,6 @@
           <t>faut pas s'étonner</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -5985,7 +6382,6 @@
           <t>Surprise</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr">
         <is>
           <t>Suggérée</t>
@@ -5996,7 +6392,6 @@
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="n">
         <v>2</v>
       </c>
@@ -6076,6 +6471,27 @@
         <v>0</v>
       </c>
       <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6188,22 +6604,16 @@
           <t>elle s'affiche si elle veut</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="n">
         <v>0</v>
       </c>
@@ -6283,6 +6693,27 @@
         <v>0</v>
       </c>
       <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6390,15 +6821,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="n">
         <v>1</v>
       </c>
@@ -6479,6 +6901,27 @@
       </c>
       <c r="BK29" t="n">
         <v>0</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -6590,22 +7033,16 @@
           <t>ca vous regarde pas</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="n">
         <v>1</v>
       </c>
@@ -6685,6 +7122,27 @@
         <v>0</v>
       </c>
       <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6797,22 +7255,16 @@
           <t>ça n'a rien d'anormal ni choquant</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="n">
         <v>3</v>
       </c>
@@ -6892,6 +7344,27 @@
         <v>0</v>
       </c>
       <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7004,22 +7477,16 @@
           <t>ils sont jaloux</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
           <t>Jalousie</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="n">
         <v>2</v>
       </c>
@@ -7099,6 +7566,27 @@
         <v>0</v>
       </c>
       <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7206,15 +7694,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="n">
         <v>1</v>
       </c>
@@ -7294,6 +7773,27 @@
         <v>0</v>
       </c>
       <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7411,7 +7911,6 @@
           <t>on s'en fou de sa vie</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
           <t>Autre</t>
@@ -7422,7 +7921,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -7433,7 +7931,6 @@
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="n">
         <v>1</v>
       </c>
@@ -7513,6 +8010,27 @@
         <v>0</v>
       </c>
       <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7625,22 +8143,16 @@
           <t>jaloux</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
           <t>Jalousie</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="n">
         <v>1</v>
       </c>
@@ -7720,6 +8232,27 @@
         <v>0</v>
       </c>
       <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7837,7 +8370,6 @@
           <t>ca reste toujours mon petit frère</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -7848,7 +8380,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -7859,7 +8390,6 @@
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="n">
         <v>1</v>
       </c>
@@ -7939,6 +8469,27 @@
         <v>0</v>
       </c>
       <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8172,6 +8723,27 @@
       <c r="BK37" t="n">
         <v>0</v>
       </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -8282,22 +8854,16 @@
           <t>et toi ta religion ? on ne t'embête pas pour savoir ce en quoi tu crois, si ?</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="n">
         <v>1</v>
       </c>
@@ -8377,6 +8943,27 @@
         <v>0</v>
       </c>
       <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8489,22 +9076,16 @@
           <t>ce n'est pas la peine qu'on s'insulte pour ça</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="n">
         <v>1</v>
       </c>
@@ -8584,6 +9165,27 @@
         <v>0</v>
       </c>
       <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8691,15 +9293,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="n">
         <v>1</v>
       </c>
@@ -8779,6 +9372,27 @@
         <v>0</v>
       </c>
       <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8891,22 +9505,16 @@
           <t>allez pas nous sortir des on s'en fou de sa vie quand vous publiez des photos de vos vieilles soirées</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="n">
         <v>0</v>
       </c>
@@ -8986,6 +9594,27 @@
         <v>0</v>
       </c>
       <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9093,15 +9722,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="n">
         <v>1</v>
       </c>
@@ -9181,6 +9801,27 @@
         <v>0</v>
       </c>
       <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9288,15 +9929,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="n">
         <v>1</v>
       </c>
@@ -9376,6 +10008,27 @@
         <v>0</v>
       </c>
       <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9488,22 +10141,16 @@
           <t>je ne te crie pas "catho" à la g si ?</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="n">
         <v>1</v>
       </c>
@@ -9584,6 +10231,27 @@
       </c>
       <c r="BK44" t="n">
         <v>0</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -9695,22 +10363,16 @@
           <t>etre méchant c'est mal</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="n">
         <v>1</v>
       </c>
@@ -9790,6 +10452,27 @@
         <v>0</v>
       </c>
       <c r="BK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9902,22 +10585,16 @@
           <t>il a vrmt un prblm</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="n">
         <v>4</v>
       </c>
@@ -9997,6 +10674,27 @@
         <v>0</v>
       </c>
       <c r="BK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10104,15 +10802,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="n">
         <v>2</v>
       </c>
@@ -10192,6 +10881,27 @@
         <v>0</v>
       </c>
       <c r="BK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10304,22 +11014,16 @@
           <t>allez vous faire foutre</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="n">
         <v>0</v>
       </c>
@@ -10399,6 +11103,27 @@
         <v>0</v>
       </c>
       <c r="BK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10511,22 +11236,16 @@
           <t>ta craqé</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr">
         <is>
           <t>Surprise</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="n">
         <v>1</v>
       </c>
@@ -10606,6 +11325,27 @@
         <v>0</v>
       </c>
       <c r="BK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10723,7 +11463,6 @@
           <t>kestu veux toi casse toi</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -10734,7 +11473,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -10745,7 +11483,6 @@
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="n">
         <v>1</v>
       </c>
@@ -10825,6 +11562,27 @@
         <v>0</v>
       </c>
       <c r="BK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10932,15 +11690,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="n">
         <v>0</v>
       </c>
@@ -11020,6 +11769,27 @@
         <v>0</v>
       </c>
       <c r="BK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11132,22 +11902,16 @@
           <t>ftg leo</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="n">
         <v>0</v>
       </c>
@@ -11227,6 +11991,27 @@
         <v>0</v>
       </c>
       <c r="BK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11339,22 +12124,16 @@
           <t>vous avez pas de vie</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr">
         <is>
           <t>Mépris</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="n">
         <v>1</v>
       </c>
@@ -11434,6 +12213,27 @@
         <v>0</v>
       </c>
       <c r="BK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11541,15 +12341,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="n">
         <v>1</v>
       </c>
@@ -11629,6 +12420,27 @@
         <v>0</v>
       </c>
       <c r="BK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11649,7 +12461,6 @@
           <t>10:41:26</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>victim</t>
@@ -11732,15 +12543,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="n">
         <v>0</v>
       </c>
@@ -11820,6 +12622,27 @@
         <v>0</v>
       </c>
       <c r="BK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11932,22 +12755,16 @@
           <t>soyez sympa come les bisou nours</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr">
         <is>
           <t>Joie</t>
         </is>
       </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="n">
         <v>2</v>
       </c>
@@ -12027,6 +12844,27 @@
         <v>0</v>
       </c>
       <c r="BK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12144,7 +12982,6 @@
           <t>de la merde</t>
         </is>
       </c>
-      <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -12155,7 +12992,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -12166,7 +13002,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="n">
         <v>2</v>
       </c>
@@ -12246,6 +13081,27 @@
         <v>0</v>
       </c>
       <c r="BK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12363,7 +13219,6 @@
           <t>la juive</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -12374,7 +13229,6 @@
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -12385,7 +13239,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="n">
         <v>2</v>
       </c>
@@ -12465,6 +13318,27 @@
         <v>0</v>
       </c>
       <c r="BK58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12577,22 +13451,16 @@
           <t>je veux pas faire bisous a un juif</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="n">
         <v>1</v>
       </c>
@@ -12672,6 +13540,27 @@
         <v>0</v>
       </c>
       <c r="BK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12905,6 +13794,27 @@
       <c r="BK60" t="n">
         <v>0</v>
       </c>
+      <c r="BL60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -13010,15 +13920,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="n">
         <v>0</v>
       </c>
@@ -13098,6 +13999,27 @@
         <v>0</v>
       </c>
       <c r="BK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13210,22 +14132,16 @@
           <t>vous en aurai jamais de toute façon</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
           <t>Dégoût</t>
         </is>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="n">
         <v>2</v>
       </c>
@@ -13305,6 +14221,27 @@
         <v>0</v>
       </c>
       <c r="BK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13412,15 +14349,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="n">
         <v>2</v>
       </c>
@@ -13500,6 +14428,27 @@
         <v>0</v>
       </c>
       <c r="BK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13733,6 +14682,27 @@
       <c r="BK64" t="n">
         <v>0</v>
       </c>
+      <c r="BL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP64" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -13848,7 +14818,6 @@
           <t>mais ça te fait quoi que je sois juive, en quoi ça te dérange ?</t>
         </is>
       </c>
-      <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -13859,7 +14828,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -13870,7 +14838,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="n">
         <v>2</v>
       </c>
@@ -13950,6 +14917,27 @@
         <v>0</v>
       </c>
       <c r="BK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14062,22 +15050,16 @@
           <t>bah regarde ailleurs alors</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr"/>
-      <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="n">
         <v>1</v>
       </c>
@@ -14158,6 +15140,27 @@
       </c>
       <c r="BK66" t="n">
         <v>0</v>
+      </c>
+      <c r="BL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO66" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -14274,7 +15277,6 @@
           <t>casse toi et arrete de parler</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -14285,7 +15287,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -14296,7 +15297,6 @@
           <t>Comportementale</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="n">
         <v>2</v>
       </c>
@@ -14376,6 +15376,27 @@
         <v>0</v>
       </c>
       <c r="BK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP67" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14488,22 +15509,16 @@
           <t>toi quand tu poste des photos on donne pa s notre avis</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="n">
         <v>0</v>
       </c>
@@ -14583,6 +15598,27 @@
         <v>0</v>
       </c>
       <c r="BK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14690,15 +15726,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr"/>
-      <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="n">
         <v>1</v>
       </c>
@@ -14778,6 +15805,27 @@
         <v>0</v>
       </c>
       <c r="BK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14890,22 +15938,16 @@
           <t>va faire ta vie si t'en a une parce que j'ai des doutes</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="n">
         <v>1</v>
       </c>
@@ -14985,6 +16027,27 @@
         <v>0</v>
       </c>
       <c r="BK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15102,7 +16165,6 @@
           <t>tu n'es  meme pas capable de répondre à ma question</t>
         </is>
       </c>
-      <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -15113,7 +16175,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr">
         <is>
           <t>Suggérée</t>
@@ -15124,7 +16185,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="n">
         <v>1</v>
       </c>
@@ -15204,6 +16264,27 @@
         <v>0</v>
       </c>
       <c r="BK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15316,22 +16397,16 @@
           <t>laisse tomber ila 0 reparti</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr"/>
-      <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="n">
         <v>2</v>
       </c>
@@ -15411,6 +16486,27 @@
         <v>0</v>
       </c>
       <c r="BK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15523,22 +16619,16 @@
           <t>ca nous dérange</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI73" t="inlineStr"/>
-      <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="n">
         <v>0</v>
       </c>
@@ -15618,6 +16708,27 @@
         <v>0</v>
       </c>
       <c r="BK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15725,15 +16836,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr"/>
-      <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
-      <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="n">
         <v>1</v>
       </c>
@@ -15813,6 +16915,27 @@
         <v>0</v>
       </c>
       <c r="BK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15920,15 +17043,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr"/>
-      <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
-      <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="n">
         <v>1</v>
       </c>
@@ -16008,6 +17122,27 @@
         <v>0</v>
       </c>
       <c r="BK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16120,22 +17255,16 @@
           <t>on aime pas les juifs</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="n">
         <v>0</v>
       </c>
@@ -16215,6 +17344,27 @@
         <v>0</v>
       </c>
       <c r="BK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16332,7 +17482,6 @@
           <t>on vs demande pas votre avis</t>
         </is>
       </c>
-      <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
           <t>Autre</t>
@@ -16343,7 +17492,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Désignée</t>
@@ -16354,7 +17502,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="n">
         <v>2</v>
       </c>
@@ -16434,6 +17581,27 @@
         <v>0</v>
       </c>
       <c r="BK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16546,22 +17714,16 @@
           <t>alors poste pas sur internet si l'avis des gens te derange</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="n">
         <v>1</v>
       </c>
@@ -16641,6 +17803,27 @@
         <v>0</v>
       </c>
       <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16758,7 +17941,6 @@
           <t>on vous laisse tranquille alors fichez nous la paix</t>
         </is>
       </c>
-      <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -16769,7 +17951,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -16780,7 +17961,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="n">
         <v>1</v>
       </c>
@@ -16860,6 +18040,27 @@
         <v>0</v>
       </c>
       <c r="BK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16967,15 +18168,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="n">
         <v>1</v>
       </c>
@@ -17055,6 +18247,27 @@
         <v>0</v>
       </c>
       <c r="BK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17167,22 +18380,16 @@
           <t>je préfère être différente que vous ressembler</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr">
         <is>
           <t>Fierté</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="n">
         <v>4</v>
       </c>
@@ -17262,6 +18469,27 @@
         <v>0</v>
       </c>
       <c r="BK81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17369,15 +18597,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="n">
         <v>2</v>
       </c>
@@ -17457,6 +18676,27 @@
         <v>0</v>
       </c>
       <c r="BK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17564,15 +18804,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="n">
         <v>2</v>
       </c>
@@ -17652,6 +18883,27 @@
         <v>0</v>
       </c>
       <c r="BK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO83" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17769,7 +19021,6 @@
           <t>elle te gene en quoi la kipa ?</t>
         </is>
       </c>
-      <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -17780,7 +19031,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr">
         <is>
           <t>Montrée</t>
@@ -17791,7 +19041,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="n">
         <v>2</v>
       </c>
@@ -17871,6 +19120,27 @@
         <v>0</v>
       </c>
       <c r="BK84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17983,22 +19253,16 @@
           <t>mdr</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr"/>
-      <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr">
         <is>
           <t>Joie</t>
         </is>
       </c>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr"/>
-      <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="n">
         <v>1</v>
       </c>
@@ -18078,6 +19342,27 @@
         <v>0</v>
       </c>
       <c r="BK85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18185,15 +19470,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr"/>
-      <c r="AC86" t="inlineStr"/>
-      <c r="AD86" t="inlineStr"/>
-      <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
-      <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="n">
         <v>0</v>
       </c>
@@ -18273,6 +19549,27 @@
         <v>0</v>
       </c>
       <c r="BK86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18390,7 +19687,6 @@
           <t>et alors</t>
         </is>
       </c>
-      <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -18401,7 +19697,6 @@
           <t>Colère</t>
         </is>
       </c>
-      <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -18412,7 +19707,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="n">
         <v>1</v>
       </c>
@@ -18493,6 +19787,27 @@
       </c>
       <c r="BK87" t="n">
         <v>0</v>
+      </c>
+      <c r="BL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -18604,22 +19919,16 @@
           <t>ET C4EST QUOI TON PRBLM AVEC LES JUIFS</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr"/>
-      <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF88" t="inlineStr"/>
-      <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr"/>
-      <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="n">
         <v>0</v>
       </c>
@@ -18699,6 +20008,27 @@
         <v>0</v>
       </c>
       <c r="BK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18806,15 +20136,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="n">
         <v>1</v>
       </c>
@@ -18894,6 +20215,27 @@
         <v>0</v>
       </c>
       <c r="BK89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19006,22 +20348,16 @@
           <t>BAS LES COUILLES</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr"/>
-      <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="n">
         <v>1</v>
       </c>
@@ -19101,6 +20437,27 @@
         <v>0</v>
       </c>
       <c r="BK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP90" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19208,15 +20565,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr"/>
-      <c r="AC91" t="inlineStr"/>
-      <c r="AD91" t="inlineStr"/>
-      <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
-      <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="n">
         <v>1</v>
       </c>
@@ -19297,6 +20645,27 @@
       </c>
       <c r="BK91" t="n">
         <v>0</v>
+      </c>
+      <c r="BL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO91" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR91" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -19408,22 +20777,16 @@
           <t>non je suis tres calme</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr"/>
-      <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="AF92" t="inlineStr"/>
-      <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI92" t="inlineStr"/>
-      <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="n">
         <v>1</v>
       </c>
@@ -19503,6 +20866,27 @@
         <v>0</v>
       </c>
       <c r="BK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19610,15 +20994,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="inlineStr"/>
-      <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="n">
         <v>1</v>
       </c>
@@ -19698,6 +21073,27 @@
         <v>0</v>
       </c>
       <c r="BK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19810,22 +21206,16 @@
           <t>ptn d'arguments</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr"/>
-      <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="n">
         <v>1</v>
       </c>
@@ -19906,6 +21296,27 @@
       </c>
       <c r="BK94" t="n">
         <v>0</v>
+      </c>
+      <c r="BL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP94" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -20017,22 +21428,16 @@
           <t>jsuis decu</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr">
         <is>
           <t>Tristesse</t>
         </is>
       </c>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr"/>
-      <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="n">
         <v>0</v>
       </c>
@@ -20112,6 +21517,27 @@
         <v>0</v>
       </c>
       <c r="BK95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20224,22 +21650,16 @@
           <t>deçu</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr">
         <is>
           <t>Tristesse</t>
         </is>
       </c>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Désignée</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="n">
         <v>1</v>
       </c>
@@ -20319,6 +21739,27 @@
         <v>0</v>
       </c>
       <c r="BK96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20431,22 +21872,16 @@
           <t>seul argumentation est qu'elle est juive</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr"/>
-      <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr">
         <is>
           <t>Suggérée</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="n">
         <v>3</v>
       </c>
@@ -20527,6 +21962,27 @@
       </c>
       <c r="BK97" t="n">
         <v>0</v>
+      </c>
+      <c r="BL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ97" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR97" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -20633,15 +22089,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="n">
         <v>1</v>
       </c>
@@ -20721,6 +22168,27 @@
         <v>0</v>
       </c>
       <c r="BK98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20828,15 +22296,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
-      <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="n">
         <v>1</v>
       </c>
@@ -20916,6 +22375,27 @@
         <v>0</v>
       </c>
       <c r="BK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21023,15 +22503,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="n">
         <v>1</v>
       </c>
@@ -21111,6 +22582,27 @@
         <v>0</v>
       </c>
       <c r="BK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21218,15 +22710,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr"/>
-      <c r="AC101" t="inlineStr"/>
-      <c r="AD101" t="inlineStr"/>
-      <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="n">
         <v>1</v>
       </c>
@@ -21306,6 +22789,27 @@
         <v>0</v>
       </c>
       <c r="BK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21413,15 +22917,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr"/>
-      <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
-      <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
-      <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="n">
         <v>2</v>
       </c>
@@ -21502,6 +22997,27 @@
       </c>
       <c r="BK102" t="n">
         <v>0</v>
+      </c>
+      <c r="BL102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO102" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -21618,7 +23134,6 @@
           <t>il a pas de vie</t>
         </is>
       </c>
-      <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="inlineStr">
         <is>
           <t>Colère</t>
@@ -21629,7 +23144,6 @@
           <t>Mépris</t>
         </is>
       </c>
-      <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr">
         <is>
           <t>Comportementale</t>
@@ -21640,7 +23154,6 @@
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="n">
         <v>3</v>
       </c>
@@ -21721,6 +23234,27 @@
       </c>
       <c r="BK103" t="n">
         <v>0</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -21832,22 +23366,16 @@
           <t>sale chien</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr">
         <is>
           <t>Colère</t>
         </is>
       </c>
-      <c r="AF104" t="inlineStr"/>
-      <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr">
         <is>
           <t>Montrée</t>
         </is>
       </c>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="n">
         <v>0</v>
       </c>
@@ -21927,6 +23455,27 @@
         <v>0</v>
       </c>
       <c r="BK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22158,6 +23707,27 @@
         <v>0</v>
       </c>
       <c r="BK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR105" t="n">
         <v>0</v>
       </c>
     </row>
